--- a/20_项目/02_光与朽项目/01_策划文档/音效资产清单.xlsx
+++ b/20_项目/02_光与朽项目/01_策划文档/音效资产清单.xlsx
@@ -900,15 +900,15 @@
     <t>game-over-417465.mp3 game-over-arcade-6435.mp3 game-over-39-199830.mp3</t>
   </si>
   <si>
+    <t>警告声音</t>
+  </si>
+  <si>
+    <t>BOSS来袭UI</t>
+  </si>
+  <si>
     <t>freesound_community-beep-warning-6387.mp3</t>
   </si>
   <si>
-    <t>警告声音</t>
-  </si>
-  <si>
-    <t>BOSS来袭UI</t>
-  </si>
-  <si>
     <t>Laser_Loop</t>
   </si>
   <si>
@@ -1250,27 +1250,7 @@
     <t>breaking-glass-84819.mp3</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>补充 - 冰冻:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 结冰的咔嚓声。当怪物被极寒光束冻住时触发。</t>
-    </r>
+    <t>补充 - 冰冻: 结冰的咔嚓声。当怪物被极寒光束冻住时触发。</t>
   </si>
   <si>
     <t>sergei_spas--435931.mp3</t>
@@ -2668,7 +2648,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2697,6 +2677,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
@@ -2741,17 +2724,11 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3128,73 +3105,73 @@
   </cols>
   <sheetData>
     <row r="1" ht="98" customHeight="1" spans="1:4">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="39" t="s">
+      <c r="C2" s="38" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" ht="49" customHeight="1" spans="1:4">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="36" t="s">
+      <c r="C3" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="40" t="s">
+      <c r="D3" s="39" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" ht="65" customHeight="1" spans="1:4">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="41" t="s">
+      <c r="C4" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="43" t="s">
+      <c r="D4" s="42" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" ht="75" customHeight="1" spans="1:4">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="42" t="s">
+      <c r="B5" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="41" t="s">
+      <c r="C5" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="40" t="s">
+      <c r="D5" s="39" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:4">
-      <c r="A6" s="41" t="s">
+      <c r="A6" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="44" t="s">
+      <c r="B6" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="41" t="s">
+      <c r="C6" s="40" t="s">
         <v>18</v>
       </c>
       <c r="D6" t="s">
@@ -3202,13 +3179,13 @@
       </c>
     </row>
     <row r="7" ht="74" customHeight="1" spans="1:4">
-      <c r="A7" s="39" t="s">
+      <c r="A7" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="36" t="s">
+      <c r="B7" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="41" t="s">
+      <c r="C7" s="40" t="s">
         <v>22</v>
       </c>
       <c r="D7" s="3" t="s">
@@ -3216,27 +3193,27 @@
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="39" t="s">
+      <c r="A8" s="38" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="39" t="s">
+      <c r="A9" s="38" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="B10" s="33" t="s">
+      <c r="B10" s="32" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="B11" s="33" t="s">
+      <c r="B11" s="32" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="B12" s="45" t="s">
+      <c r="B12" s="44" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3282,10 +3259,10 @@
       <c r="A2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="C2" s="29" t="s">
         <v>34</v>
       </c>
       <c r="D2" s="4" t="s">
@@ -3296,10 +3273,10 @@
       <c r="A3" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="30" t="s">
         <v>38</v>
       </c>
       <c r="D3" t="s">
@@ -3310,10 +3287,10 @@
       <c r="A4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="29" t="s">
         <v>42</v>
       </c>
       <c r="D4" s="4" t="s">
@@ -3324,10 +3301,10 @@
       <c r="A5" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="30" t="s">
+      <c r="C5" s="29" t="s">
         <v>46</v>
       </c>
       <c r="D5" s="4" t="s">
@@ -3338,10 +3315,10 @@
       <c r="A6" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="31" t="s">
+      <c r="B6" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="31" t="s">
+      <c r="C6" s="30" t="s">
         <v>50</v>
       </c>
       <c r="D6" t="s">
@@ -3367,7 +3344,7 @@
       <c r="B13" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C13" s="30" t="s">
+      <c r="C13" s="29" t="s">
         <v>56</v>
       </c>
       <c r="D13" s="4" t="s">
@@ -3381,134 +3358,134 @@
       <c r="B14" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="C14" s="29" t="s">
         <v>60</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="15" s="13" customFormat="1" ht="29.55" spans="1:4">
+    <row r="15" s="14" customFormat="1" ht="29.55" spans="1:4">
       <c r="A15" s="5" t="s">
         <v>62</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C15" s="31" t="s">
+      <c r="C15" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="14" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="16" s="13" customFormat="1" ht="15.15" spans="1:4">
+    <row r="16" s="14" customFormat="1" ht="15.15" spans="1:4">
       <c r="A16" s="5" t="s">
         <v>66</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C16" s="31" t="s">
+      <c r="C16" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="14" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="17" s="13" customFormat="1" ht="29.55" spans="1:4">
+    <row r="17" s="14" customFormat="1" ht="29.55" spans="1:4">
       <c r="A17" s="5" t="s">
         <v>70</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C17" s="31" t="s">
+      <c r="C17" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="D17" s="32" t="s">
+      <c r="D17" s="31" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="18" s="13" customFormat="1" ht="29.55" spans="1:4">
+    <row r="18" s="14" customFormat="1" ht="29.55" spans="1:4">
       <c r="A18" s="5" t="s">
         <v>74</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C18" s="31" t="s">
+      <c r="C18" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="14" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="19" s="13" customFormat="1" ht="43.95" spans="1:4">
+    <row r="19" s="14" customFormat="1" ht="43.95" spans="1:4">
       <c r="A19" s="5" t="s">
         <v>78</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C19" s="31" t="s">
+      <c r="C19" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="D19" s="32" t="s">
+      <c r="D19" s="31" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="20" s="13" customFormat="1" ht="15.15" spans="1:4">
+    <row r="20" s="14" customFormat="1" ht="15.15" spans="1:4">
       <c r="A20" s="5" t="s">
         <v>82</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C20" s="31" t="s">
+      <c r="C20" s="30" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="33" t="s">
+      <c r="A21" s="32" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="34" t="s">
+      <c r="A22" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="33" t="s">
+      <c r="A23" s="32" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="34" t="s">
+      <c r="A24" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="35"/>
-      <c r="B25" s="35"/>
+      <c r="A25" s="34"/>
+      <c r="B25" s="34"/>
       <c r="C25" s="3"/>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="35"/>
-      <c r="B26" s="35"/>
+      <c r="A26" s="34"/>
+      <c r="B26" s="34"/>
       <c r="C26" s="3"/>
     </row>
     <row r="27" ht="57.6" spans="1:4">
-      <c r="A27" s="36" t="s">
+      <c r="A27" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="B27" s="36" t="s">
+      <c r="B27" s="35" t="s">
         <v>90</v>
       </c>
       <c r="C27" s="3" t="s">
@@ -3516,26 +3493,25 @@
       </c>
     </row>
     <row r="28" ht="28.8" spans="1:4">
-      <c r="A28" s="36" t="s">
+      <c r="A28" s="35" t="s">
         <v>92</v>
       </c>
-      <c r="B28" s="37" t="s">
+      <c r="B28" s="36" t="s">
         <v>93</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
-      <c r="D29" t="s">
+    <row r="30" spans="1:4">
+      <c r="A30" s="10" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" t="s">
+      <c r="B30" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" s="10"/>
+      <c r="D30" s="10" t="s">
         <v>97</v>
       </c>
     </row>
@@ -3661,44 +3637,44 @@
         <v>123</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="8" t="s">
+    <row r="9" ht="28.8" spans="1:4">
+      <c r="A9" s="8"/>
+      <c r="B9" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9" t="s">
+      <c r="C9" s="10"/>
+      <c r="D9" s="10" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="12" t="s">
+      <c r="B10" s="12"/>
+      <c r="C10" s="13" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="14" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="14" t="s">
         <v>133</v>
       </c>
     </row>
@@ -3706,10 +3682,10 @@
       <c r="A13" t="s">
         <v>134</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="C13" s="9"/>
+      <c r="C13" s="10"/>
       <c r="D13" s="4" t="s">
         <v>136</v>
       </c>
@@ -3718,10 +3694,10 @@
       <c r="A14" t="s">
         <v>137</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="C14" s="9"/>
+      <c r="C14" s="10"/>
       <c r="D14" t="s">
         <v>139</v>
       </c>
@@ -3730,10 +3706,10 @@
       <c r="A15" t="s">
         <v>140</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="C15" s="9"/>
+      <c r="C15" s="10"/>
       <c r="D15" s="4" t="s">
         <v>142</v>
       </c>
@@ -3742,10 +3718,10 @@
       <c r="A16" t="s">
         <v>143</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="C16" s="9"/>
+      <c r="C16" s="10"/>
     </row>
     <row r="17" ht="15.15"/>
     <row r="18" ht="15.15" spans="1:5">
@@ -3766,7 +3742,7 @@
       <c r="B19" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="16" t="s">
         <v>147</v>
       </c>
       <c r="D19" s="4" t="s">
@@ -3802,13 +3778,13 @@
       </c>
     </row>
     <row r="22" ht="29.55" spans="1:5">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="17" t="s">
         <v>157</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C22" s="16" t="s">
         <v>159</v>
       </c>
       <c r="D22" s="4" t="s">
@@ -3819,21 +3795,21 @@
       <c r="A23" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C23" s="18" t="s">
+      <c r="C23" s="19" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="24" ht="15.15" spans="1:5">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="C24" s="20" t="s">
         <v>166</v>
       </c>
     </row>
@@ -3847,7 +3823,7 @@
       <c r="C25" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="D25" s="20" t="s">
+      <c r="D25" s="21" t="s">
         <v>170</v>
       </c>
     </row>
@@ -3855,10 +3831,10 @@
       <c r="A26" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="B26" s="21" t="s">
+      <c r="B26" s="22" t="s">
         <v>172</v>
       </c>
-      <c r="C26" s="19" t="s">
+      <c r="C26" s="20" t="s">
         <v>173</v>
       </c>
     </row>
@@ -3866,10 +3842,10 @@
       <c r="A27" t="s">
         <v>174</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="C27" s="9"/>
+      <c r="C27" s="10"/>
       <c r="D27" s="4" t="s">
         <v>176</v>
       </c>
@@ -3878,19 +3854,20 @@
       <c r="A28" t="s">
         <v>177</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="C28" s="9"/>
+      <c r="C28" s="10"/>
       <c r="D28" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="30" ht="28.8" spans="1:5">
-      <c r="B30" s="4" t="s">
+      <c r="A30" s="10"/>
+      <c r="B30" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="10" t="s">
         <v>181</v>
       </c>
       <c r="D30" s="4" t="s">
@@ -3898,10 +3875,10 @@
       </c>
     </row>
     <row r="31" ht="28.8" spans="1:5">
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="10" t="s">
         <v>184</v>
       </c>
       <c r="D31" s="4" t="s">
@@ -3912,18 +3889,18 @@
       </c>
     </row>
     <row r="32" ht="28.8" spans="1:5">
-      <c r="B32" s="22" t="s">
+      <c r="B32" s="23" t="s">
         <v>187</v>
       </c>
-      <c r="C32" s="23" t="s">
+      <c r="C32" s="24" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="33" ht="28.8" spans="2:4">
-      <c r="B33" t="s">
+      <c r="B33" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="10" t="s">
         <v>190</v>
       </c>
       <c r="D33" s="4" t="s">
@@ -3931,10 +3908,10 @@
       </c>
     </row>
     <row r="34" spans="2:4">
-      <c r="B34" t="s">
+      <c r="B34" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="10" t="s">
         <v>193</v>
       </c>
       <c r="D34" t="s">
@@ -3953,18 +3930,18 @@
       </c>
     </row>
     <row r="36" ht="28.8" spans="2:4">
-      <c r="B36" s="22" t="s">
+      <c r="B36" s="23" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="23" t="s">
+      <c r="C36" s="24" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="37" ht="28.8" spans="2:4">
-      <c r="B37" s="24" t="s">
+      <c r="B37" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="C37" s="9" t="s">
+      <c r="C37" s="10" t="s">
         <v>201</v>
       </c>
       <c r="D37" t="s">
@@ -3980,10 +3957,10 @@
       </c>
     </row>
     <row r="41" ht="43.2" spans="2:4">
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="10" t="s">
         <v>206</v>
       </c>
       <c r="D41" s="4" t="s">
@@ -3991,26 +3968,26 @@
       </c>
     </row>
     <row r="42" ht="28.8" spans="2:4">
-      <c r="B42" s="22" t="s">
+      <c r="B42" s="23" t="s">
         <v>208</v>
       </c>
-      <c r="C42" s="23" t="s">
+      <c r="C42" s="24" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="43" spans="2:4">
-      <c r="B43" s="23" t="s">
+      <c r="B43" s="24" t="s">
         <v>210</v>
       </c>
-      <c r="C43" s="23" t="s">
+      <c r="C43" s="24" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="44" ht="28.8" spans="2:4">
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="10" t="s">
         <v>213</v>
       </c>
       <c r="D44" t="s">
@@ -4018,18 +3995,18 @@
       </c>
     </row>
     <row r="45" ht="28.8" spans="2:4">
-      <c r="B45" s="22" t="s">
+      <c r="B45" s="23" t="s">
         <v>215</v>
       </c>
-      <c r="C45" s="23" t="s">
+      <c r="C45" s="24" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="46" ht="43.2" spans="2:4">
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="10" t="s">
         <v>218</v>
       </c>
       <c r="D46" t="s">
@@ -4037,10 +4014,10 @@
       </c>
     </row>
     <row r="47" ht="28.8" spans="2:4">
-      <c r="B47" s="24" t="s">
+      <c r="B47" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="C47" s="9" t="s">
+      <c r="C47" s="10" t="s">
         <v>221</v>
       </c>
       <c r="D47" t="s">
@@ -4048,10 +4025,10 @@
       </c>
     </row>
     <row r="48" ht="28.8" spans="2:4">
-      <c r="B48" s="27" t="s">
+      <c r="B48" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="C48" s="14" t="s">
+      <c r="C48" s="15" t="s">
         <v>224</v>
       </c>
       <c r="D48" t="s">
@@ -4059,18 +4036,18 @@
       </c>
     </row>
     <row r="49" ht="28.8" spans="2:4">
-      <c r="B49" s="28" t="s">
+      <c r="B49" s="27" t="s">
         <v>225</v>
       </c>
-      <c r="C49" s="23" t="s">
+      <c r="C49" s="24" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="50" ht="28.8" spans="2:4">
-      <c r="B50" s="22" t="s">
+      <c r="B50" s="23" t="s">
         <v>227</v>
       </c>
-      <c r="C50" s="23" t="s">
+      <c r="C50" s="24" t="s">
         <v>228</v>
       </c>
     </row>
@@ -4083,19 +4060,19 @@
       </c>
     </row>
     <row r="52" ht="43.2" spans="2:4">
-      <c r="B52" s="24" t="s">
+      <c r="B52" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="C52" s="9" t="s">
+      <c r="C52" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="D52" s="9"/>
+      <c r="D52" s="10"/>
     </row>
     <row r="53" spans="2:4">
-      <c r="B53" t="s">
+      <c r="B53" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="10" t="s">
         <v>234</v>
       </c>
       <c r="D53" t="s">
